--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.34272907492474</v>
+        <v>9.155693474675271</v>
       </c>
       <c r="D2" t="n">
-        <v>24.05742273079278</v>
+        <v>3.909331193753828</v>
       </c>
       <c r="E2" t="n">
-        <v>6.973268964238304</v>
+        <v>1.133156206688724</v>
       </c>
       <c r="F2" t="n">
-        <v>23.57116514052557</v>
+        <v>3.830314335335404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.28926700340135</v>
+        <v>11.42200588805272</v>
       </c>
       <c r="D3" t="n">
-        <v>71.19975301184391</v>
+        <v>11.56995986442464</v>
       </c>
       <c r="E3" t="n">
-        <v>6.973268964238304</v>
+        <v>1.133156206688724</v>
       </c>
       <c r="F3" t="n">
-        <v>23.57116514052557</v>
+        <v>3.830314335335404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
